--- a/China NEA/review_workbooks/2024-05-06_2024年一季度光伏发电建设情况---国家能源局_review.xlsx
+++ b/China NEA/review_workbooks/2024-05-06_2024年一季度光伏发电建设情况---国家能源局_review.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,42 +439,1546 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>65950</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37950</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12294</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>111.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>547.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>309.1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>313.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5712.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3210.3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2501.6</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1773.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>151.8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>48.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2642.3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1927.6</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>714.7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>512.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>323.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>247.6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6015.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1669.1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4346.4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2629.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>340.3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>310.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2681.8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2471.6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>210.2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>68.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1037.6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>531.9</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>505.6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>266.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>482.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>347.1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>135.4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>578.1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>396.1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>182.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>43.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>308.3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>268.5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>21.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>492.7</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>444.9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>203.3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4420.8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1203.6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3217.1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1062.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>240.3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>221.2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3597.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>686.2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2910.8</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>253.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>209.4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>178.8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3432.5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1316.6</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2115.9</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1035.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>99.8</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>99.2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>974.3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>44.7</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>929.6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>362.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>126.6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2119.9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1052.6</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1067.3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>590.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>147.9</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>147.8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>35.4</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>3879.2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>630.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3249.3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2266.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>84.1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2700.1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1840.2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>859.9</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>303.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1341.4</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>413.6</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>927.8</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>313.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>188.4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>96.7</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>659.8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>603.4</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>40.4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2348.8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1826.9</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>521.9</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>292.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>162.9</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2681.7</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2563.3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>118.4</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>117.9</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2658.1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2638.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>98.3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2242.1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2109.8</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>206.9</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>206.5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3149.6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3131.20</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>新疆兵团</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>47.1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>47.1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>273.5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>273.5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>271.2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>266.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>157.9</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>33.6</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>124.3</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2926.4</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1224.5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1701.9</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>242.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>186.1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>37.8</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>148.3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1319.0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>854.5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>464.5</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>159.1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>649.4</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>468.9</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>180.5</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>82.1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1729.8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1696.5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>198.7</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>163.5</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>35.3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2270.5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2101.3</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>169.1</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25.1</t>
         </is>
       </c>
     </row>
@@ -755,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,30 +2331,1278 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>457</v>
+        <v>4574</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>2193</v>
       </c>
       <c r="E2" t="n">
-        <v>219</v>
+        <v>2381</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>692</v>
       </c>
       <c r="G2" t="n">
+        <v>65950</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37950</v>
+      </c>
+      <c r="I2" t="n">
+        <v>28000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12294</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>106</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tianjin</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>547.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="I4" t="n">
         <v>238</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>69</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="b">
+      <c r="J4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hebei</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>313.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>204</v>
+      </c>
+      <c r="E5" t="n">
+        <v>109</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5712</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3210.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2501.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1773.7</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Shanxi</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2642.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1927.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>714.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>512.6</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Shandong</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>323</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>247.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6015.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1669.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4346.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2629</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Inner Mongolia</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>310</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2681.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2471.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Liaoning</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>48</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1037.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>531.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>505.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>266</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jilin</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>482.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Heilongjiang</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>578.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>396.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>182</v>
+      </c>
+      <c r="J11" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>308.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jiangsu</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>492.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>203.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4420.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1203.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3217.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1062.6</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Zhejiang</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3597</v>
+      </c>
+      <c r="H14" t="n">
+        <v>686.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2910.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Anhui</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>209.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3432.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1316.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2115.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1035.5</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fujian</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22</v>
+      </c>
+      <c r="G16" t="n">
+        <v>974.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>929.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jiangxi</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2119.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1052.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1067.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>590.2</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Henan</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3879.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>630</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3249.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2266.6</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hubei</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2700.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1840.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>859.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>303.4</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hunan</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1341.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>413.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>927.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chongqing</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sichuan</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>659.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>603.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Shaanxi</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2348.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1826.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>521.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>292.1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gansu</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2681.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2563.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Qinghai</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>117</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2658.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2638</v>
+      </c>
+      <c r="I25" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ningxia</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2242.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2109.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Xinjiang</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>206.9</v>
+      </c>
+      <c r="D27" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3149.6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3131.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>新疆兵团</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Xinjiang Production and Construction Corps</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tibet</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>271.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>124.3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2926.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1224.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1701.9</v>
+      </c>
+      <c r="J30" t="n">
+        <v>242.1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Guangxi</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1319</v>
+      </c>
+      <c r="H31" t="n">
+        <v>854.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>464.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>19</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hainan</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>177</v>
+      </c>
+      <c r="D32" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>649.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>468.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Guizhou</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="D33" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1729.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1696.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Yunnan</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>198.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2270.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2101.3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="K34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -865,7 +3617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,30 +3803,1278 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>457</v>
+        <v>4574</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2193</v>
       </c>
       <c r="E4" t="n">
-        <v>219</v>
+        <v>2381</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>692</v>
       </c>
       <c r="G4" t="n">
+        <v>65950</v>
+      </c>
+      <c r="H4" t="n">
+        <v>37950</v>
+      </c>
+      <c r="I4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12294</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>106</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tianjin</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>547.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="I6" t="n">
         <v>238</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>69</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="b">
+      <c r="J6" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hebei</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>313.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>204</v>
+      </c>
+      <c r="E7" t="n">
+        <v>109</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5712</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3210.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2501.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1773.7</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Shanxi</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2642.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1927.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>714.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>512.6</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Shandong</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>323</v>
+      </c>
+      <c r="D9" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>247.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6015.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1669.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4346.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2629</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Inner Mongolia</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>310</v>
+      </c>
+      <c r="E10" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2681.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2471.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Liaoning</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>48</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1037.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>531.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>505.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>266</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jilin</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>482.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Heilongjiang</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>578.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>396.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>182</v>
+      </c>
+      <c r="J13" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>308.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jiangsu</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>492.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>203.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4420.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1203.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3217.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1062.6</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Zhejiang</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3597</v>
+      </c>
+      <c r="H16" t="n">
+        <v>686.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2910.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Anhui</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>209.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3432.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1316.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2115.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1035.5</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fujian</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22</v>
+      </c>
+      <c r="G18" t="n">
+        <v>974.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>929.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jiangxi</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2119.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1052.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1067.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>590.2</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Henan</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3879.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>630</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3249.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2266.6</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hubei</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>16</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2700.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1840.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>859.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>303.4</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hunan</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1341.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>413.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>927.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Chongqing</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sichuan</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>659.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>603.4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Shaanxi</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2348.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1826.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>521.9</v>
+      </c>
+      <c r="J25" t="n">
+        <v>292.1</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gansu</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2681.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2563.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Qinghai</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D27" t="n">
+        <v>117</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2658.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2638</v>
+      </c>
+      <c r="I27" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ningxia</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2242.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2109.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Xinjiang</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>206.9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3149.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3131.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>新疆兵团</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Xinjiang Production and Construction Corps</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tibet</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>271.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="D32" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>124.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2926.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1224.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1701.9</v>
+      </c>
+      <c r="J32" t="n">
+        <v>242.1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Guangxi</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1319</v>
+      </c>
+      <c r="H33" t="n">
+        <v>854.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>464.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>19</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hainan</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>177</v>
+      </c>
+      <c r="D34" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>649.4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>468.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Guizhou</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="D35" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1729.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1696.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Yunnan</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>198.7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2270.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2101.3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="K36" t="b">
         <v>0</v>
       </c>
     </row>
